--- a/Outcome/Appendix/Tables/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Tables/Joinpoint_APC_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">DateRange</t>
   </si>
@@ -60,21 +60,6 @@
   </si>
   <si>
     <t xml:space="preserve">2021/05~2025/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2013/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2013/11~2016/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016/08~2025/12</t>
   </si>
 </sst>
 </file>
@@ -543,66 +528,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-40.27</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-52.25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-25.28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
